--- a/astro-site/public/dl/plan-catering-tematico-eventos/calculadora-pricing-catering-tematico-eventos.xlsx
+++ b/astro-site/public/dl/plan-catering-tematico-eventos/calculadora-pricing-catering-tematico-eventos.xlsx
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Entrega sin servicio: una persona lleva y monta; la empresa paga la factura (sin anticipo). Si en la entrega va alcohol o refrescos con azúcar añadido, esa parte va al 21 % de IVA.</t>
+          <t>Entrega sin servicio: una persona lleva y monta; la empresa paga la factura (sin anticipo). Si en la entrega va alcohol o refrescos, zumos y gaseosas con azúcares o edulcorantes añadidos, esa parte va al 21 % de IVA.</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2195,7 @@
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>El catering con servicio va al 10 % de IVA, alcohol incluido (Ley 37/1992, art. 91.Uno.2.2.º). En una entrega sin servicio, la comida sigue al 10 % pero el alcohol y los refrescos con azúcar añadido van al 21 %. El menaje, la mantelería y la cristalería que facturas junto con el catering siguen al servicio principal; si facturas aparte mobiliario, carpas o decoración, esa línea va al 21 %.</t>
+          <t>El catering con servicio va al 10 % de IVA, alcohol incluido (Ley 37/1992, art. 91.Uno.2.2.º). En una entrega sin servicio, la comida sigue al 10 % pero el alcohol y los refrescos, zumos y gaseosas con azúcares o edulcorantes añadidos van al 21 %. El menaje, la mantelería y la cristalería que facturas junto con el catering siguen al servicio principal; si facturas aparte mobiliario, carpas o decoración, esa línea va al 21 %.</t>
         </is>
       </c>
     </row>
